--- a/Elenco_Concorso_TOTALE_marzo 2026.xlsx
+++ b/Elenco_Concorso_TOTALE_marzo 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elisa/Desktop/LAVORI/MOKADOR/CONCORSO/Elenco locali-negozi/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g.moroni\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C19EDA1-F2CE-2B49-A1FC-64A3310AD280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC92BD3-52E9-409D-BBC4-F9B0EEEE2DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6580" yWindow="1840" windowWidth="41200" windowHeight="24640" xr2:uid="{823CA8BD-5CB5-43A5-84D0-940CC410799D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{823CA8BD-5CB5-43A5-84D0-940CC410799D}"/>
   </bookViews>
   <sheets>
     <sheet name="Elenco locali e negozi" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="17" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4478" uniqueCount="2589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4495" uniqueCount="2595">
   <si>
     <t>B &amp; B di BRANDOLINI ENRICO E C. SAS</t>
   </si>
@@ -7800,18 +7800,43 @@
   </si>
   <si>
     <t>Via San Silvestro, 176</t>
+  </si>
+  <si>
+    <t>GEMOS SOC. COOP</t>
+  </si>
+  <si>
+    <t>BAR VILLA ERBOSA</t>
+  </si>
+  <si>
+    <t>VIA DELL' ARCOVEGGIO, 50/2</t>
+  </si>
+  <si>
+    <t>BONTAVOLA SAN LAZZARO</t>
+  </si>
+  <si>
+    <t>VIA EMILIA, 268/A</t>
+  </si>
+  <si>
+    <t>SAN LAZZARO DI SAVENA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -7893,11 +7918,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -7905,55 +7930,63 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -15035,7 +15068,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A75AFA3-FD86-B247-89D1-E3D6D435196F}" name="Tabella pivot1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A75AFA3-FD86-B247-89D1-E3D6D435196F}" name="Tabella pivot1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0">
@@ -15787,9 +15820,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -15827,7 +15860,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -15933,7 +15966,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -16075,7 +16108,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -16083,20 +16116,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147308C3-0088-488A-BBC3-4C05F360FB79}">
-  <dimension ref="A1:H637"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H643"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="123.42578125" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="51.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="6" max="6" width="51.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>120</v>
       </c>
@@ -16122,7 +16155,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -16148,7 +16181,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -16174,7 +16207,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -16200,7 +16233,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -16226,7 +16259,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -16252,7 +16285,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -16278,7 +16311,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -16304,7 +16337,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -16330,7 +16363,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -16356,7 +16389,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -16382,7 +16415,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -16408,7 +16441,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -16434,7 +16467,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -16460,7 +16493,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -16486,7 +16519,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -16512,7 +16545,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -16538,7 +16571,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -16564,7 +16597,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -16590,7 +16623,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -16616,7 +16649,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -16642,7 +16675,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1</v>
       </c>
@@ -16668,7 +16701,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1</v>
       </c>
@@ -16694,7 +16727,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1</v>
       </c>
@@ -16720,7 +16753,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -16746,7 +16779,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1</v>
       </c>
@@ -16772,7 +16805,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1</v>
       </c>
@@ -16798,7 +16831,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>1</v>
       </c>
@@ -16824,7 +16857,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -16850,7 +16883,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>1</v>
       </c>
@@ -16876,7 +16909,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>1</v>
       </c>
@@ -16902,7 +16935,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1</v>
       </c>
@@ -16928,7 +16961,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>1</v>
       </c>
@@ -16954,7 +16987,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>1</v>
       </c>
@@ -16980,7 +17013,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>1</v>
       </c>
@@ -17006,7 +17039,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>1</v>
       </c>
@@ -17032,7 +17065,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1</v>
       </c>
@@ -17058,7 +17091,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1</v>
       </c>
@@ -17084,7 +17117,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1</v>
       </c>
@@ -17110,7 +17143,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1</v>
       </c>
@@ -17136,7 +17169,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1</v>
       </c>
@@ -17162,7 +17195,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1</v>
       </c>
@@ -17188,7 +17221,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1</v>
       </c>
@@ -17214,7 +17247,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1</v>
       </c>
@@ -17240,7 +17273,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1</v>
       </c>
@@ -17266,7 +17299,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1</v>
       </c>
@@ -17292,7 +17325,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1</v>
       </c>
@@ -17318,7 +17351,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1</v>
       </c>
@@ -17344,7 +17377,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1</v>
       </c>
@@ -17370,7 +17403,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1</v>
       </c>
@@ -17396,7 +17429,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1</v>
       </c>
@@ -17422,7 +17455,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1</v>
       </c>
@@ -17448,7 +17481,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1</v>
       </c>
@@ -17474,7 +17507,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>96</v>
       </c>
@@ -17500,7 +17533,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>95</v>
       </c>
@@ -17526,7 +17559,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>95</v>
       </c>
@@ -17552,7 +17585,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>95</v>
       </c>
@@ -17578,7 +17611,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>95</v>
       </c>
@@ -17604,7 +17637,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>95</v>
       </c>
@@ -17630,7 +17663,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -17656,7 +17689,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -17682,7 +17715,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>95</v>
       </c>
@@ -17708,7 +17741,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>95</v>
       </c>
@@ -17734,7 +17767,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>95</v>
       </c>
@@ -17760,7 +17793,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>95</v>
       </c>
@@ -17786,7 +17819,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>95</v>
       </c>
@@ -17812,7 +17845,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>95</v>
       </c>
@@ -17838,7 +17871,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>95</v>
       </c>
@@ -17864,7 +17897,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>95</v>
       </c>
@@ -17890,7 +17923,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>95</v>
       </c>
@@ -17916,7 +17949,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>95</v>
       </c>
@@ -17942,7 +17975,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>95</v>
       </c>
@@ -17968,7 +18001,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>95</v>
       </c>
@@ -17994,7 +18027,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>95</v>
       </c>
@@ -18020,7 +18053,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>95</v>
       </c>
@@ -18046,7 +18079,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>95</v>
       </c>
@@ -18072,7 +18105,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>95</v>
       </c>
@@ -18098,7 +18131,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>95</v>
       </c>
@@ -18124,7 +18157,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>95</v>
       </c>
@@ -18150,7 +18183,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>95</v>
       </c>
@@ -18176,7 +18209,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>95</v>
       </c>
@@ -18202,7 +18235,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>95</v>
       </c>
@@ -18228,7 +18261,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>95</v>
       </c>
@@ -18254,7 +18287,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -18280,7 +18313,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>95</v>
       </c>
@@ -18306,7 +18339,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>95</v>
       </c>
@@ -18332,7 +18365,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>95</v>
       </c>
@@ -18358,7 +18391,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>95</v>
       </c>
@@ -18384,7 +18417,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>95</v>
       </c>
@@ -18410,7 +18443,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>95</v>
       </c>
@@ -18436,7 +18469,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>95</v>
       </c>
@@ -18462,7 +18495,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -18488,7 +18521,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -18514,7 +18547,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -18540,7 +18573,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>95</v>
       </c>
@@ -18566,7 +18599,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -18592,7 +18625,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>395</v>
       </c>
@@ -18618,7 +18651,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>395</v>
       </c>
@@ -18644,7 +18677,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>407</v>
       </c>
@@ -18670,7 +18703,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>395</v>
       </c>
@@ -18696,7 +18729,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>407</v>
       </c>
@@ -18722,7 +18755,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>407</v>
       </c>
@@ -18748,7 +18781,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>407</v>
       </c>
@@ -18774,7 +18807,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>407</v>
       </c>
@@ -18800,7 +18833,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>407</v>
       </c>
@@ -18826,7 +18859,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>407</v>
       </c>
@@ -18852,7 +18885,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>407</v>
       </c>
@@ -18878,7 +18911,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>407</v>
       </c>
@@ -18904,7 +18937,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>407</v>
       </c>
@@ -18930,7 +18963,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>407</v>
       </c>
@@ -18956,7 +18989,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>407</v>
       </c>
@@ -18982,7 +19015,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>407</v>
       </c>
@@ -19008,7 +19041,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>407</v>
       </c>
@@ -19034,7 +19067,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>489</v>
       </c>
@@ -19060,7 +19093,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>489</v>
       </c>
@@ -19086,7 +19119,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>489</v>
       </c>
@@ -19112,7 +19145,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>489</v>
       </c>
@@ -19138,7 +19171,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>489</v>
       </c>
@@ -19164,7 +19197,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>489</v>
       </c>
@@ -19190,7 +19223,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>489</v>
       </c>
@@ -19216,7 +19249,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>489</v>
       </c>
@@ -19242,7 +19275,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>489</v>
       </c>
@@ -19268,7 +19301,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>489</v>
       </c>
@@ -19294,7 +19327,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>489</v>
       </c>
@@ -19320,7 +19353,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>489</v>
       </c>
@@ -19346,7 +19379,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>489</v>
       </c>
@@ -19372,7 +19405,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>489</v>
       </c>
@@ -19398,7 +19431,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>489</v>
       </c>
@@ -19424,7 +19457,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>489</v>
       </c>
@@ -19450,7 +19483,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>489</v>
       </c>
@@ -19476,7 +19509,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>489</v>
       </c>
@@ -19502,7 +19535,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>489</v>
       </c>
@@ -19528,7 +19561,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>489</v>
       </c>
@@ -19554,7 +19587,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>489</v>
       </c>
@@ -19580,7 +19613,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>489</v>
       </c>
@@ -19606,7 +19639,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>489</v>
       </c>
@@ -19632,7 +19665,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>489</v>
       </c>
@@ -19658,7 +19691,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>489</v>
       </c>
@@ -19684,7 +19717,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>489</v>
       </c>
@@ -19710,7 +19743,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>489</v>
       </c>
@@ -19736,7 +19769,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>489</v>
       </c>
@@ -19762,7 +19795,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>489</v>
       </c>
@@ -19788,7 +19821,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>489</v>
       </c>
@@ -19814,7 +19847,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>489</v>
       </c>
@@ -19840,7 +19873,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>489</v>
       </c>
@@ -19866,7 +19899,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>489</v>
       </c>
@@ -19892,7 +19925,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>489</v>
       </c>
@@ -19918,7 +19951,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>489</v>
       </c>
@@ -19944,7 +19977,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>489</v>
       </c>
@@ -19970,7 +20003,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>489</v>
       </c>
@@ -19996,7 +20029,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>489</v>
       </c>
@@ -20022,7 +20055,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>489</v>
       </c>
@@ -20048,7 +20081,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>489</v>
       </c>
@@ -20074,7 +20107,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>489</v>
       </c>
@@ -20100,7 +20133,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>489</v>
       </c>
@@ -20126,7 +20159,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>489</v>
       </c>
@@ -20152,7 +20185,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>489</v>
       </c>
@@ -20178,7 +20211,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>489</v>
       </c>
@@ -20204,7 +20237,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>489</v>
       </c>
@@ -20230,7 +20263,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>489</v>
       </c>
@@ -20256,7 +20289,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>489</v>
       </c>
@@ -20282,7 +20315,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>717</v>
       </c>
@@ -20308,7 +20341,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>717</v>
       </c>
@@ -20334,7 +20367,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>717</v>
       </c>
@@ -20360,7 +20393,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>717</v>
       </c>
@@ -20386,7 +20419,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>717</v>
       </c>
@@ -20412,7 +20445,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>717</v>
       </c>
@@ -20438,7 +20471,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>717</v>
       </c>
@@ -20464,7 +20497,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>717</v>
       </c>
@@ -20490,7 +20523,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>717</v>
       </c>
@@ -20516,7 +20549,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>717</v>
       </c>
@@ -20542,7 +20575,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>717</v>
       </c>
@@ -20568,7 +20601,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>717</v>
       </c>
@@ -20594,7 +20627,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>717</v>
       </c>
@@ -20620,7 +20653,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>717</v>
       </c>
@@ -20646,7 +20679,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>780</v>
       </c>
@@ -20672,7 +20705,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>780</v>
       </c>
@@ -20698,7 +20731,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>780</v>
       </c>
@@ -20724,7 +20757,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>780</v>
       </c>
@@ -20750,7 +20783,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>780</v>
       </c>
@@ -20776,7 +20809,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>780</v>
       </c>
@@ -20802,7 +20835,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>780</v>
       </c>
@@ -20828,7 +20861,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>780</v>
       </c>
@@ -20854,7 +20887,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>780</v>
       </c>
@@ -20880,7 +20913,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>780</v>
       </c>
@@ -20906,7 +20939,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>780</v>
       </c>
@@ -20932,7 +20965,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>780</v>
       </c>
@@ -20958,7 +20991,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>780</v>
       </c>
@@ -20984,7 +21017,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>780</v>
       </c>
@@ -21010,7 +21043,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>780</v>
       </c>
@@ -21036,7 +21069,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>780</v>
       </c>
@@ -21062,7 +21095,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>780</v>
       </c>
@@ -21088,7 +21121,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>780</v>
       </c>
@@ -21114,7 +21147,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>780</v>
       </c>
@@ -21140,7 +21173,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>780</v>
       </c>
@@ -21166,7 +21199,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>780</v>
       </c>
@@ -21192,7 +21225,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>780</v>
       </c>
@@ -21218,7 +21251,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>780</v>
       </c>
@@ -21244,7 +21277,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>780</v>
       </c>
@@ -21270,7 +21303,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>780</v>
       </c>
@@ -21296,7 +21329,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>780</v>
       </c>
@@ -21322,7 +21355,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>780</v>
       </c>
@@ -21348,7 +21381,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>780</v>
       </c>
@@ -21374,7 +21407,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>780</v>
       </c>
@@ -21400,7 +21433,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>780</v>
       </c>
@@ -21426,7 +21459,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>780</v>
       </c>
@@ -21452,7 +21485,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>780</v>
       </c>
@@ -21478,7 +21511,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>780</v>
       </c>
@@ -21504,7 +21537,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>780</v>
       </c>
@@ -21530,7 +21563,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>780</v>
       </c>
@@ -21556,7 +21589,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>780</v>
       </c>
@@ -21582,7 +21615,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>780</v>
       </c>
@@ -21608,7 +21641,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>780</v>
       </c>
@@ -21634,7 +21667,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>780</v>
       </c>
@@ -21660,7 +21693,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>780</v>
       </c>
@@ -21686,7 +21719,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>780</v>
       </c>
@@ -21712,7 +21745,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>780</v>
       </c>
@@ -21738,7 +21771,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>780</v>
       </c>
@@ -21764,7 +21797,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>780</v>
       </c>
@@ -21790,7 +21823,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>780</v>
       </c>
@@ -21816,7 +21849,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>780</v>
       </c>
@@ -21842,7 +21875,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>780</v>
       </c>
@@ -21868,7 +21901,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>780</v>
       </c>
@@ -21894,7 +21927,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>978</v>
       </c>
@@ -21920,7 +21953,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>978</v>
       </c>
@@ -21946,7 +21979,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>978</v>
       </c>
@@ -21972,7 +22005,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>978</v>
       </c>
@@ -21998,7 +22031,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>978</v>
       </c>
@@ -22024,7 +22057,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>978</v>
       </c>
@@ -22050,7 +22083,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>978</v>
       </c>
@@ -22076,7 +22109,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>978</v>
       </c>
@@ -22102,7 +22135,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>978</v>
       </c>
@@ -22128,7 +22161,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>978</v>
       </c>
@@ -22154,7 +22187,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>978</v>
       </c>
@@ -22180,7 +22213,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>978</v>
       </c>
@@ -22206,7 +22239,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>978</v>
       </c>
@@ -22232,7 +22265,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>978</v>
       </c>
@@ -22258,7 +22291,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>978</v>
       </c>
@@ -22284,7 +22317,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>978</v>
       </c>
@@ -22310,7 +22343,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>978</v>
       </c>
@@ -22336,7 +22369,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>978</v>
       </c>
@@ -22362,7 +22395,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>978</v>
       </c>
@@ -22388,7 +22421,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>978</v>
       </c>
@@ -22414,7 +22447,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>978</v>
       </c>
@@ -22440,7 +22473,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>978</v>
       </c>
@@ -22466,7 +22499,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>978</v>
       </c>
@@ -22492,7 +22525,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>978</v>
       </c>
@@ -22518,7 +22551,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>978</v>
       </c>
@@ -22544,7 +22577,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>978</v>
       </c>
@@ -22570,7 +22603,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>978</v>
       </c>
@@ -22596,7 +22629,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>978</v>
       </c>
@@ -22622,7 +22655,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>978</v>
       </c>
@@ -22648,7 +22681,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>978</v>
       </c>
@@ -22674,7 +22707,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>978</v>
       </c>
@@ -22700,7 +22733,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>978</v>
       </c>
@@ -22726,7 +22759,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>978</v>
       </c>
@@ -22752,7 +22785,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>978</v>
       </c>
@@ -22778,7 +22811,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>978</v>
       </c>
@@ -22804,7 +22837,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>978</v>
       </c>
@@ -22830,7 +22863,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>978</v>
       </c>
@@ -22856,7 +22889,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>978</v>
       </c>
@@ -22882,7 +22915,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>978</v>
       </c>
@@ -22908,7 +22941,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>978</v>
       </c>
@@ -22934,7 +22967,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>978</v>
       </c>
@@ -22960,7 +22993,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>978</v>
       </c>
@@ -22986,7 +23019,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>978</v>
       </c>
@@ -23012,7 +23045,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>978</v>
       </c>
@@ -23038,7 +23071,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>978</v>
       </c>
@@ -23064,7 +23097,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>978</v>
       </c>
@@ -23090,7 +23123,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>978</v>
       </c>
@@ -23116,7 +23149,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>978</v>
       </c>
@@ -23142,7 +23175,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>978</v>
       </c>
@@ -23168,7 +23201,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>978</v>
       </c>
@@ -23194,7 +23227,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>978</v>
       </c>
@@ -23220,7 +23253,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>978</v>
       </c>
@@ -23246,7 +23279,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>978</v>
       </c>
@@ -23272,7 +23305,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>978</v>
       </c>
@@ -23298,7 +23331,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>717</v>
       </c>
@@ -23324,7 +23357,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>489</v>
       </c>
@@ -23350,7 +23383,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>780</v>
       </c>
@@ -23376,7 +23409,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="281" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="5" t="s">
         <v>1218</v>
       </c>
@@ -23402,7 +23435,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="5" t="s">
         <v>1218</v>
       </c>
@@ -23428,7 +23461,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="5" t="s">
         <v>1218</v>
       </c>
@@ -23454,7 +23487,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="5" t="s">
         <v>1218</v>
       </c>
@@ -23480,7 +23513,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="5" t="s">
         <v>1218</v>
       </c>
@@ -23506,7 +23539,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="286" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="5" t="s">
         <v>1219</v>
       </c>
@@ -23532,7 +23565,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="5" t="s">
         <v>1219</v>
       </c>
@@ -23558,7 +23591,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="5" t="s">
         <v>1219</v>
       </c>
@@ -23584,7 +23617,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="5" t="s">
         <v>1220</v>
       </c>
@@ -23610,7 +23643,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="5" t="s">
         <v>1220</v>
       </c>
@@ -23636,7 +23669,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="5" t="s">
         <v>1220</v>
       </c>
@@ -23662,7 +23695,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="292" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="5" t="s">
         <v>1220</v>
       </c>
@@ -23688,7 +23721,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="293" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="5" t="s">
         <v>1220</v>
       </c>
@@ -23714,7 +23747,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="294" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="5" t="s">
         <v>1220</v>
       </c>
@@ -23740,7 +23773,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="5" t="s">
         <v>1218</v>
       </c>
@@ -23766,7 +23799,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="296" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="5" t="s">
         <v>1220</v>
       </c>
@@ -23792,7 +23825,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="5" t="s">
         <v>1220</v>
       </c>
@@ -23818,7 +23851,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="298" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="5" t="s">
         <v>1218</v>
       </c>
@@ -23844,7 +23877,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="299" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="5" t="s">
         <v>1218</v>
       </c>
@@ -23870,7 +23903,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="300" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="5" t="s">
         <v>1218</v>
       </c>
@@ -23896,7 +23929,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="301" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="5" t="s">
         <v>1218</v>
       </c>
@@ -23922,7 +23955,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="302" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="5" t="s">
         <v>1218</v>
       </c>
@@ -23948,7 +23981,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="5" t="s">
         <v>1218</v>
       </c>
@@ -23974,7 +24007,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="304" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="5" t="s">
         <v>1220</v>
       </c>
@@ -24000,7 +24033,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="305" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24026,7 +24059,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="306" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24052,7 +24085,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="307" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24078,7 +24111,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="308" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24104,7 +24137,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="309" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="5" t="s">
         <v>1219</v>
       </c>
@@ -24130,7 +24163,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="310" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="5" t="s">
         <v>1219</v>
       </c>
@@ -24156,7 +24189,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="311" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="5" t="s">
         <v>1219</v>
       </c>
@@ -24182,7 +24215,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="312" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="5" t="s">
         <v>1219</v>
       </c>
@@ -24208,7 +24241,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="313" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="5" t="s">
         <v>1219</v>
       </c>
@@ -24234,7 +24267,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="314" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24260,7 +24293,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="315" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="5" t="s">
         <v>1220</v>
       </c>
@@ -24286,7 +24319,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="316" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="5" t="s">
         <v>1220</v>
       </c>
@@ -24312,7 +24345,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="317" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24338,7 +24371,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="318" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24364,7 +24397,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="319" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24390,7 +24423,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="320" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24416,7 +24449,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="321" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24442,7 +24475,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="322" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24468,7 +24501,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="323" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24494,7 +24527,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="324" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24520,7 +24553,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="325" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24546,7 +24579,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="326" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24572,7 +24605,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="327" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="5" t="s">
         <v>1218</v>
       </c>
@@ -24598,7 +24631,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="328" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="5" t="s">
         <v>1221</v>
       </c>
@@ -24624,7 +24657,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24650,7 +24683,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24676,7 +24709,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="331" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24702,7 +24735,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="332" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24728,7 +24761,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="333" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24754,7 +24787,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="334" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24780,7 +24813,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="335" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24806,7 +24839,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24832,7 +24865,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="337" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24858,7 +24891,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="338" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24884,7 +24917,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="339" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24910,7 +24943,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="340" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24936,7 +24969,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24962,7 +24995,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="5" t="s">
         <v>1222</v>
       </c>
@@ -24988,7 +25021,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="5" t="s">
         <v>1222</v>
       </c>
@@ -25014,7 +25047,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="5" t="s">
         <v>1222</v>
       </c>
@@ -25040,7 +25073,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="5" t="s">
         <v>1222</v>
       </c>
@@ -25066,7 +25099,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25092,7 +25125,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25118,7 +25151,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25144,7 +25177,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25170,7 +25203,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25196,7 +25229,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25222,7 +25255,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25248,7 +25281,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="353" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25274,7 +25307,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="354" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25300,7 +25333,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="355" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25326,7 +25359,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25352,7 +25385,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25378,7 +25411,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25404,7 +25437,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25430,7 +25463,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25456,7 +25489,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25482,7 +25515,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="362" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25508,7 +25541,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="363" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25534,7 +25567,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25560,7 +25593,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25586,7 +25619,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25612,7 +25645,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25638,7 +25671,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25664,7 +25697,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25690,7 +25723,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25716,7 +25749,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25742,7 +25775,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25768,7 +25801,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" s="5" t="s">
         <v>1223</v>
       </c>
@@ -25794,7 +25827,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="374" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" s="6" t="s">
         <v>1224</v>
       </c>
@@ -25820,7 +25853,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="375" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" s="5" t="s">
         <v>1220</v>
       </c>
@@ -25846,7 +25879,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="376" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" s="5" t="s">
         <v>1220</v>
       </c>
@@ -25872,7 +25905,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="377" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" s="5" t="s">
         <v>1220</v>
       </c>
@@ -25898,7 +25931,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="378" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" s="5" t="s">
         <v>1218</v>
       </c>
@@ -25924,7 +25957,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="379" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" s="5" t="s">
         <v>1220</v>
       </c>
@@ -25950,7 +25983,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="380" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" s="5" t="s">
         <v>1218</v>
       </c>
@@ -25976,7 +26009,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="381" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26002,7 +26035,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="382" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26028,7 +26061,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="383" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26054,7 +26087,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="384" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26080,7 +26113,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="385" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26106,7 +26139,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="386" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26132,7 +26165,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="387" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26158,7 +26191,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="388" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26184,7 +26217,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="389" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26210,7 +26243,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="390" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26236,7 +26269,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="391" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26262,7 +26295,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="392" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26288,7 +26321,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="393" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26314,7 +26347,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="394" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26340,7 +26373,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="395" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26366,7 +26399,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="396" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26392,7 +26425,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="397" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26418,7 +26451,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="398" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26444,7 +26477,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="399" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26470,7 +26503,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="400" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26496,7 +26529,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="401" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26522,7 +26555,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="402" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26548,7 +26581,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="403" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26574,7 +26607,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="404" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26600,7 +26633,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="405" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26626,7 +26659,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="406" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26652,7 +26685,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="407" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26678,7 +26711,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="408" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26704,7 +26737,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="409" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26730,7 +26763,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="410" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26756,7 +26789,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="411" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26782,7 +26815,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="412" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" s="5" t="s">
         <v>1220</v>
       </c>
@@ -26808,7 +26841,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="413" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" s="5" t="s">
         <v>1225</v>
       </c>
@@ -26834,7 +26867,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="414" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" s="5" t="s">
         <v>1219</v>
       </c>
@@ -26860,7 +26893,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="415" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" s="5" t="s">
         <v>1225</v>
       </c>
@@ -26886,7 +26919,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="416" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26912,7 +26945,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="417" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" s="5" t="s">
         <v>1225</v>
       </c>
@@ -26938,7 +26971,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="418" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" s="5" t="s">
         <v>1219</v>
       </c>
@@ -26964,7 +26997,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="419" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" s="5" t="s">
         <v>1218</v>
       </c>
@@ -26990,7 +27023,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="420" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" s="5" t="s">
         <v>1218</v>
       </c>
@@ -27016,7 +27049,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="421" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" s="5" t="s">
         <v>1219</v>
       </c>
@@ -27042,7 +27075,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="422" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" s="5" t="s">
         <v>1225</v>
       </c>
@@ -27068,7 +27101,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="423" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" s="5" t="s">
         <v>1225</v>
       </c>
@@ -27094,7 +27127,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="424" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" s="5" t="s">
         <v>1219</v>
       </c>
@@ -27120,7 +27153,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="425" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" s="5" t="s">
         <v>1225</v>
       </c>
@@ -27146,7 +27179,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="426" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" s="5" t="s">
         <v>1219</v>
       </c>
@@ -27172,7 +27205,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="427" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" s="5" t="s">
         <v>1219</v>
       </c>
@@ -27198,7 +27231,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="428" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" s="5" t="s">
         <v>1219</v>
       </c>
@@ -27224,7 +27257,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="429" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" s="5" t="s">
         <v>1219</v>
       </c>
@@ -27250,7 +27283,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="430" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" s="5" t="s">
         <v>1219</v>
       </c>
@@ -27276,7 +27309,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="431" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27302,7 +27335,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="432" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27328,7 +27361,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="433" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27354,7 +27387,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="434" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" s="5" t="s">
         <v>1222</v>
       </c>
@@ -27380,7 +27413,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="435" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27406,7 +27439,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="436" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27432,7 +27465,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="437" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27458,7 +27491,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="438" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27484,7 +27517,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="439" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27510,7 +27543,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="440" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27536,7 +27569,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="441" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27562,7 +27595,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="442" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27588,7 +27621,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="443" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27614,7 +27647,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="444" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27640,7 +27673,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="445" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27666,7 +27699,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="446" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27692,7 +27725,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="447" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27718,7 +27751,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="448" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27744,7 +27777,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="449" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27770,7 +27803,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="450" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27796,7 +27829,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="451" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27822,7 +27855,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="452" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27848,7 +27881,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="453" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27874,7 +27907,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="454" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27900,7 +27933,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="455" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27926,7 +27959,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="456" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27952,7 +27985,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="457" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" s="5" t="s">
         <v>1226</v>
       </c>
@@ -27978,7 +28011,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="458" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28004,7 +28037,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="459" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28030,7 +28063,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="460" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28056,7 +28089,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="461" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28082,7 +28115,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="462" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28108,7 +28141,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="463" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28134,7 +28167,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="464" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28160,7 +28193,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="465" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28186,7 +28219,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="466" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28212,7 +28245,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="467" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28238,7 +28271,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="468" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28264,7 +28297,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="469" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28290,7 +28323,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="470" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28316,7 +28349,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="471" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28342,7 +28375,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="472" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28368,7 +28401,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="473" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28394,7 +28427,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="474" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28420,7 +28453,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="475" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28446,7 +28479,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="476" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28472,7 +28505,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="477" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28498,7 +28531,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="478" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28524,7 +28557,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="479" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" s="5" t="s">
         <v>1226</v>
       </c>
@@ -28550,7 +28583,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="480" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="5" t="s">
         <v>1225</v>
       </c>
@@ -28576,7 +28609,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="481" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" s="5" t="s">
         <v>1218</v>
       </c>
@@ -28602,7 +28635,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="482" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" s="5" t="s">
         <v>1225</v>
       </c>
@@ -28628,7 +28661,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="483" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" s="5" t="s">
         <v>1225</v>
       </c>
@@ -28654,7 +28687,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="484" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" s="5" t="s">
         <v>1225</v>
       </c>
@@ -28680,7 +28713,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="485" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" s="5" t="s">
         <v>1225</v>
       </c>
@@ -28706,7 +28739,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="486" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" s="5" t="s">
         <v>1218</v>
       </c>
@@ -28732,7 +28765,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="487" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" s="5" t="s">
         <v>1219</v>
       </c>
@@ -28758,7 +28791,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="488" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" s="5" t="s">
         <v>1219</v>
       </c>
@@ -28784,7 +28817,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="489" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" s="5" t="s">
         <v>1219</v>
       </c>
@@ -28810,7 +28843,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="490" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" s="5" t="s">
         <v>1225</v>
       </c>
@@ -28836,7 +28869,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="491" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" s="5" t="s">
         <v>1225</v>
       </c>
@@ -28862,7 +28895,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="492" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" s="5" t="s">
         <v>1225</v>
       </c>
@@ -28888,7 +28921,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="493" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" s="5" t="s">
         <v>1225</v>
       </c>
@@ -28914,7 +28947,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="494" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" s="5" t="s">
         <v>1225</v>
       </c>
@@ -28940,7 +28973,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="495" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" s="5" t="s">
         <v>1225</v>
       </c>
@@ -28966,7 +28999,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="496" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" s="5" t="s">
         <v>1225</v>
       </c>
@@ -28992,7 +29025,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="497" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29018,7 +29051,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="498" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29044,7 +29077,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="499" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" s="5" t="s">
         <v>1219</v>
       </c>
@@ -29070,7 +29103,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="500" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" s="5" t="s">
         <v>1219</v>
       </c>
@@ -29096,7 +29129,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="501" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29122,7 +29155,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="502" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29148,7 +29181,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="503" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29174,7 +29207,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="504" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29200,7 +29233,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="505" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29226,7 +29259,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="506" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29252,7 +29285,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="507" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29278,7 +29311,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="508" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29304,7 +29337,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="509" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29330,7 +29363,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="510" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" s="5" t="s">
         <v>1219</v>
       </c>
@@ -29356,7 +29389,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="511" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29382,7 +29415,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="512" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29408,7 +29441,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="513" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="5" t="s">
         <v>1219</v>
       </c>
@@ -29434,7 +29467,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="514" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29460,7 +29493,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="515" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="5" t="s">
         <v>1218</v>
       </c>
@@ -29486,7 +29519,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="516" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="5" t="s">
         <v>1225</v>
       </c>
@@ -29512,7 +29545,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="517" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="5" t="s">
         <v>1218</v>
       </c>
@@ -29538,7 +29571,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="518" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="5" t="s">
         <v>1218</v>
       </c>
@@ -29564,7 +29597,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="519" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="5" t="s">
         <v>1221</v>
       </c>
@@ -29590,7 +29623,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="520" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="5" t="s">
         <v>1221</v>
       </c>
@@ -29616,7 +29649,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="521" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="5" t="s">
         <v>1221</v>
       </c>
@@ -29642,7 +29675,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="522" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="5" t="s">
         <v>1221</v>
       </c>
@@ -29668,7 +29701,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="523" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="5" t="s">
         <v>1221</v>
       </c>
@@ -29694,7 +29727,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="524" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="5" t="s">
         <v>1221</v>
       </c>
@@ -29720,7 +29753,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="525" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="5" t="s">
         <v>1221</v>
       </c>
@@ -29746,7 +29779,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="526" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" s="5" t="s">
         <v>1221</v>
       </c>
@@ -29772,7 +29805,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="527" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" s="5" t="s">
         <v>1221</v>
       </c>
@@ -29798,7 +29831,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="528" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" s="5" t="s">
         <v>1221</v>
       </c>
@@ -29824,7 +29857,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="529" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" s="5" t="s">
         <v>1221</v>
       </c>
@@ -29850,7 +29883,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" s="5" t="s">
         <v>1219</v>
       </c>
@@ -29876,7 +29909,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" s="5" t="s">
         <v>1218</v>
       </c>
@@ -29902,7 +29935,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" s="5" t="s">
         <v>1220</v>
       </c>
@@ -29928,7 +29961,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" s="5" t="s">
         <v>1226</v>
       </c>
@@ -29954,7 +29987,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" s="5" t="s">
         <v>1218</v>
       </c>
@@ -29980,7 +30013,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30006,7 +30039,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" s="5" t="s">
         <v>1220</v>
       </c>
@@ -30032,7 +30065,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30058,7 +30091,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" s="5" t="s">
         <v>1219</v>
       </c>
@@ -30084,7 +30117,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" s="5" t="s">
         <v>1219</v>
       </c>
@@ -30110,7 +30143,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30136,7 +30169,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" s="5" t="s">
         <v>1226</v>
       </c>
@@ -30162,7 +30195,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" s="5" t="s">
         <v>1220</v>
       </c>
@@ -30188,7 +30221,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" s="5" t="s">
         <v>1220</v>
       </c>
@@ -30214,7 +30247,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30240,7 +30273,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" s="5" t="s">
         <v>1220</v>
       </c>
@@ -30266,7 +30299,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30292,7 +30325,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" s="5" t="s">
         <v>1226</v>
       </c>
@@ -30318,7 +30351,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" s="5" t="s">
         <v>1220</v>
       </c>
@@ -30344,7 +30377,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" s="5" t="s">
         <v>1220</v>
       </c>
@@ -30370,7 +30403,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" s="5" t="s">
         <v>1226</v>
       </c>
@@ -30396,7 +30429,7 @@
         <v>2278</v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" s="5" t="s">
         <v>1225</v>
       </c>
@@ -30422,7 +30455,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="552" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" s="5" t="s">
         <v>1226</v>
       </c>
@@ -30448,7 +30481,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" s="5" t="s">
         <v>1220</v>
       </c>
@@ -30474,7 +30507,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" s="5" t="s">
         <v>1220</v>
       </c>
@@ -30500,7 +30533,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" s="5" t="s">
         <v>1220</v>
       </c>
@@ -30526,7 +30559,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30552,7 +30585,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" s="5" t="s">
         <v>1226</v>
       </c>
@@ -30578,7 +30611,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" s="5" t="s">
         <v>1222</v>
       </c>
@@ -30604,7 +30637,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" s="5" t="s">
         <v>1222</v>
       </c>
@@ -30630,7 +30663,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30656,7 +30689,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" s="5" t="s">
         <v>1220</v>
       </c>
@@ -30682,7 +30715,7 @@
         <v>2328</v>
       </c>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30708,7 +30741,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" s="5" t="s">
         <v>1226</v>
       </c>
@@ -30734,7 +30767,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" s="5" t="s">
         <v>1220</v>
       </c>
@@ -30760,7 +30793,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30786,7 +30819,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30812,7 +30845,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30838,7 +30871,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="568" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30864,7 +30897,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="569" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30890,7 +30923,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="570" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30916,7 +30949,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="571" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" s="5" t="s">
         <v>1218</v>
       </c>
@@ -30942,7 +30975,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" s="5" t="s">
         <v>1225</v>
       </c>
@@ -30968,7 +31001,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" s="5" t="s">
         <v>1225</v>
       </c>
@@ -30994,7 +31027,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" s="5" t="s">
         <v>1226</v>
       </c>
@@ -31020,7 +31053,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" s="5" t="s">
         <v>1221</v>
       </c>
@@ -31046,7 +31079,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" s="5" t="s">
         <v>1221</v>
       </c>
@@ -31072,7 +31105,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" s="5" t="s">
         <v>1221</v>
       </c>
@@ -31098,7 +31131,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="578" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" s="5" t="s">
         <v>1221</v>
       </c>
@@ -31124,7 +31157,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" s="5" t="s">
         <v>1221</v>
       </c>
@@ -31150,7 +31183,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" s="5" t="s">
         <v>1221</v>
       </c>
@@ -31176,7 +31209,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" s="5" t="s">
         <v>1221</v>
       </c>
@@ -31202,7 +31235,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" s="5" t="s">
         <v>1220</v>
       </c>
@@ -31228,7 +31261,7 @@
         <v>2382</v>
       </c>
     </row>
-    <row r="583" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" s="5" t="s">
         <v>1220</v>
       </c>
@@ -31254,7 +31287,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" s="5" t="s">
         <v>1219</v>
       </c>
@@ -31280,7 +31313,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" s="5" t="s">
         <v>1226</v>
       </c>
@@ -31306,7 +31339,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" s="5" t="s">
         <v>1219</v>
       </c>
@@ -31332,7 +31365,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" s="5" t="s">
         <v>1219</v>
       </c>
@@ -31358,7 +31391,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="588" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" s="5" t="s">
         <v>1219</v>
       </c>
@@ -31384,7 +31417,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" s="5" t="s">
         <v>1219</v>
       </c>
@@ -31410,7 +31443,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" s="5" t="s">
         <v>1226</v>
       </c>
@@ -31436,7 +31469,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" s="5" t="s">
         <v>1218</v>
       </c>
@@ -31462,7 +31495,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A592" s="5" t="s">
         <v>1218</v>
       </c>
@@ -31488,7 +31521,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" s="5" t="s">
         <v>1218</v>
       </c>
@@ -31514,7 +31547,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A594" s="5" t="s">
         <v>1218</v>
       </c>
@@ -31540,7 +31573,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A595" s="5" t="s">
         <v>1225</v>
       </c>
@@ -31566,7 +31599,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A596" s="5" t="s">
         <v>1225</v>
       </c>
@@ -31592,7 +31625,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" s="5" t="s">
         <v>1219</v>
       </c>
@@ -31618,7 +31651,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="598" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" s="5" t="s">
         <v>1219</v>
       </c>
@@ -31644,7 +31677,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A599" s="5" t="s">
         <v>1219</v>
       </c>
@@ -31670,7 +31703,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A600" s="5" t="s">
         <v>1218</v>
       </c>
@@ -31696,7 +31729,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A601" s="5" t="s">
         <v>1226</v>
       </c>
@@ -31722,7 +31755,7 @@
         <v>2278</v>
       </c>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A602" s="5" t="s">
         <v>1223</v>
       </c>
@@ -31748,7 +31781,7 @@
         <v>2458</v>
       </c>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A603" s="5" t="s">
         <v>1226</v>
       </c>
@@ -31774,7 +31807,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A604" s="5" t="s">
         <v>1219</v>
       </c>
@@ -31800,7 +31833,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" s="5" t="s">
         <v>1226</v>
       </c>
@@ -31826,7 +31859,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" s="5" t="s">
         <v>1226</v>
       </c>
@@ -31852,7 +31885,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" s="5" t="s">
         <v>1226</v>
       </c>
@@ -31878,7 +31911,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="608" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" s="5" t="s">
         <v>1226</v>
       </c>
@@ -31904,7 +31937,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="609" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609" s="5" t="s">
         <v>1225</v>
       </c>
@@ -31930,7 +31963,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" s="5" t="s">
         <v>1225</v>
       </c>
@@ -31956,7 +31989,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" s="5" t="s">
         <v>1225</v>
       </c>
@@ -31982,7 +32015,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" s="5" t="s">
         <v>1225</v>
       </c>
@@ -32008,7 +32041,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" s="5" t="s">
         <v>1225</v>
       </c>
@@ -32034,7 +32067,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" s="5" t="s">
         <v>1226</v>
       </c>
@@ -32060,7 +32093,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" s="5" t="s">
         <v>1226</v>
       </c>
@@ -32086,7 +32119,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" s="5" t="s">
         <v>1226</v>
       </c>
@@ -32112,7 +32145,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" s="5" t="s">
         <v>1226</v>
       </c>
@@ -32138,7 +32171,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" s="5" t="s">
         <v>1218</v>
       </c>
@@ -32164,7 +32197,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" s="5" t="s">
         <v>1219</v>
       </c>
@@ -32190,7 +32223,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" s="5" t="s">
         <v>1226</v>
       </c>
@@ -32216,7 +32249,7 @@
         <v>2278</v>
       </c>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" s="5" t="s">
         <v>1226</v>
       </c>
@@ -32242,7 +32275,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" s="5" t="s">
         <v>1218</v>
       </c>
@@ -32268,7 +32301,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" s="5" t="s">
         <v>1219</v>
       </c>
@@ -32294,7 +32327,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="624" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" s="5" t="s">
         <v>1226</v>
       </c>
@@ -32320,7 +32353,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" s="5" t="s">
         <v>1225</v>
       </c>
@@ -32346,7 +32379,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" s="5" t="s">
         <v>1225</v>
       </c>
@@ -32372,7 +32405,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" s="5" t="s">
         <v>1219</v>
       </c>
@@ -32398,7 +32431,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" s="5" t="s">
         <v>1219</v>
       </c>
@@ -32424,7 +32457,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" s="5" t="s">
         <v>1219</v>
       </c>
@@ -32450,7 +32483,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" s="5" t="s">
         <v>1226</v>
       </c>
@@ -32476,7 +32509,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" s="5" t="s">
         <v>1226</v>
       </c>
@@ -32502,7 +32535,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" s="5" t="s">
         <v>1223</v>
       </c>
@@ -32528,7 +32561,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" s="5" t="s">
         <v>1223</v>
       </c>
@@ -32554,7 +32587,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" s="6" t="s">
         <v>1224</v>
       </c>
@@ -32580,7 +32613,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" s="5" t="s">
         <v>1220</v>
       </c>
@@ -32606,7 +32639,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" s="6" t="s">
         <v>1224</v>
       </c>
@@ -32632,7 +32665,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" s="6" t="s">
         <v>1224</v>
       </c>
@@ -32657,6 +32690,76 @@
       <c r="H637" s="5" t="s">
         <v>68</v>
       </c>
+    </row>
+    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A638" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B638" s="22">
+        <v>12274</v>
+      </c>
+      <c r="C638" s="23" t="s">
+        <v>2589</v>
+      </c>
+      <c r="D638" s="23" t="s">
+        <v>2590</v>
+      </c>
+      <c r="E638" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="F638" s="23" t="s">
+        <v>2591</v>
+      </c>
+      <c r="G638" s="23" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H638" s="23" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="639" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A639" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B639" s="22">
+        <v>12274</v>
+      </c>
+      <c r="C639" s="23" t="s">
+        <v>2589</v>
+      </c>
+      <c r="D639" s="23" t="s">
+        <v>2592</v>
+      </c>
+      <c r="E639" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="F639" s="23" t="s">
+        <v>2593</v>
+      </c>
+      <c r="G639" t="s">
+        <v>2594</v>
+      </c>
+      <c r="H639" s="23" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A640" s="6" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="641" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A641" s="6" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A642" s="6" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="643" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A643" s="21"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H280" xr:uid="{147308C3-0088-488A-BBC3-4C05F360FB79}"/>
@@ -32664,7 +32767,7 @@
     <sortCondition ref="A2:A6410"/>
     <sortCondition ref="C2:C6410"/>
   </sortState>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D468" r:id="rId1" xr:uid="{D5A630AF-B453-0D43-AF40-702A22EAE263}"/>
     <hyperlink ref="D389" r:id="rId2" display="https://restaurantguru.it/Piquadro-Caffe-Cialde-e-capsule-Ciampino-2" xr:uid="{B5CA2E5D-59B1-C048-B6BB-9493D987F226}"/>
@@ -32677,614 +32780,614 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B719FAE0-9EC0-B744-9D10-33D5A397E661}">
   <dimension ref="A3:B22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="48" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="18" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="21" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="13" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="18" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="24" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="26" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="13" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="27.83203125" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="61" max="62" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="62" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="72" max="72" width="15" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="28" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="87" max="88" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="27.83203125" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="87" max="88" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="92" max="92" width="17" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="102" max="102" width="22" bestFit="1" customWidth="1"/>
     <col min="103" max="103" width="31" bestFit="1" customWidth="1"/>
     <col min="104" max="104" width="18" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="106" max="106" width="37" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="33.5" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="109" max="109" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="111" max="111" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="112" max="112" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="114" max="115" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="116" max="116" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="118" max="118" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="120" max="120" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="121" max="121" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="122" max="122" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="123" max="123" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="114" max="115" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="123" max="123" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="124" max="124" width="23" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="127" max="127" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="128" max="128" width="14" bestFit="1" customWidth="1"/>
-    <col min="129" max="129" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="130" max="130" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="131" max="131" width="41.5" bestFit="1" customWidth="1"/>
+    <col min="129" max="129" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="132" max="132" width="13" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="134" max="134" width="18" bestFit="1" customWidth="1"/>
-    <col min="135" max="135" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="135" max="135" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="136" max="136" width="17" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="138" max="139" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="138" max="139" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="140" max="140" width="21" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="143" max="143" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="144" max="144" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="145" max="146" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="147" max="147" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="143" max="143" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="144" max="144" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="145" max="146" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="147" max="147" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="148" max="148" width="16" bestFit="1" customWidth="1"/>
     <col min="149" max="149" width="15" bestFit="1" customWidth="1"/>
-    <col min="150" max="150" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="151" max="151" width="12" bestFit="1" customWidth="1"/>
-    <col min="152" max="152" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="153" max="153" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="154" max="154" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="156" max="156" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="157" max="157" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="158" max="158" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="159" max="159" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="152" max="152" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="153" max="153" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="154" max="154" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="156" max="156" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="157" max="157" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="158" max="158" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="159" max="159" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="160" max="160" width="15" bestFit="1" customWidth="1"/>
-    <col min="161" max="161" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="162" max="162" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="161" max="161" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="162" max="162" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="163" max="163" width="15" bestFit="1" customWidth="1"/>
-    <col min="164" max="165" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="166" max="166" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="167" max="167" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="168" max="168" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="164" max="165" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="166" max="166" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="167" max="167" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="168" max="168" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="169" max="169" width="16" bestFit="1" customWidth="1"/>
-    <col min="170" max="170" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="171" max="171" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="172" max="172" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="173" max="173" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="170" max="170" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="171" max="171" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="172" max="172" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="173" max="173" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="174" max="174" width="16" bestFit="1" customWidth="1"/>
-    <col min="175" max="175" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="176" max="176" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="177" max="177" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="178" max="178" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="179" max="179" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="180" max="180" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="181" max="181" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="182" max="182" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="183" max="183" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="175" max="175" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="176" max="176" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="177" max="177" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="178" max="178" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="179" max="179" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="180" max="180" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="181" max="181" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="182" max="182" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="183" max="183" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="184" max="184" width="23" bestFit="1" customWidth="1"/>
-    <col min="185" max="185" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="186" max="186" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="187" max="187" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="188" max="188" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="185" max="185" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="186" max="186" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="187" max="187" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="188" max="188" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="189" max="189" width="20" bestFit="1" customWidth="1"/>
-    <col min="190" max="190" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="190" max="190" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="191" max="191" width="17" bestFit="1" customWidth="1"/>
-    <col min="192" max="192" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="193" max="193" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="194" max="194" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="195" max="195" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="192" max="192" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="193" max="193" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="194" max="194" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="195" max="195" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="196" max="196" width="14" bestFit="1" customWidth="1"/>
-    <col min="197" max="197" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="198" max="198" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="199" max="200" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="201" max="201" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="202" max="202" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="203" max="203" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="204" max="204" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="197" max="197" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="198" max="198" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="199" max="200" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="201" max="201" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="202" max="202" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="203" max="203" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="204" max="204" width="34.7109375" bestFit="1" customWidth="1"/>
     <col min="205" max="205" width="18" bestFit="1" customWidth="1"/>
-    <col min="206" max="206" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="207" max="207" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="206" max="206" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="207" max="207" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="208" max="208" width="34" bestFit="1" customWidth="1"/>
-    <col min="209" max="210" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="211" max="211" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="212" max="212" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="213" max="213" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="214" max="214" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="215" max="215" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="216" max="216" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="217" max="217" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="218" max="218" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="219" max="219" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="209" max="210" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="211" max="211" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="212" max="212" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="213" max="213" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="214" max="214" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="215" max="215" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="216" max="216" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="217" max="217" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="218" max="218" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="219" max="219" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="220" max="220" width="12" bestFit="1" customWidth="1"/>
-    <col min="221" max="221" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="222" max="222" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="223" max="224" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="225" max="225" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="226" max="226" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="227" max="227" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="228" max="228" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="221" max="221" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="222" max="222" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="223" max="224" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="225" max="225" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="226" max="226" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="227" max="227" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="228" max="228" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="229" max="229" width="21" bestFit="1" customWidth="1"/>
     <col min="230" max="230" width="20" bestFit="1" customWidth="1"/>
-    <col min="231" max="231" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="232" max="232" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="233" max="233" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="234" max="234" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="235" max="235" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="236" max="236" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="237" max="237" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="238" max="238" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="239" max="239" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="240" max="240" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="241" max="241" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="242" max="242" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="243" max="243" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="231" max="231" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="232" max="232" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="233" max="233" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="234" max="234" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="235" max="235" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="236" max="236" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="237" max="237" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="238" max="238" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="239" max="239" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="240" max="240" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="241" max="241" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="242" max="242" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="243" max="243" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="244" max="244" width="15" bestFit="1" customWidth="1"/>
-    <col min="245" max="245" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="246" max="246" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="245" max="245" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="246" max="246" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="247" max="247" width="19" bestFit="1" customWidth="1"/>
     <col min="248" max="248" width="18" bestFit="1" customWidth="1"/>
-    <col min="249" max="249" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="250" max="250" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="251" max="251" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="249" max="249" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="250" max="250" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="251" max="251" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="252" max="252" width="17" bestFit="1" customWidth="1"/>
     <col min="253" max="253" width="21" bestFit="1" customWidth="1"/>
-    <col min="254" max="254" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="255" max="255" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="256" max="256" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="257" max="257" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="258" max="258" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="259" max="259" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="260" max="260" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="261" max="261" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="254" max="254" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="255" max="255" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="256" max="256" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="257" max="257" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="258" max="258" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="259" max="259" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="260" max="260" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="261" max="261" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="262" max="262" width="18" bestFit="1" customWidth="1"/>
-    <col min="263" max="263" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="264" max="264" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="265" max="266" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="263" max="263" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="264" max="264" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="265" max="266" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="267" max="267" width="23" bestFit="1" customWidth="1"/>
-    <col min="268" max="268" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="269" max="269" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="270" max="270" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="271" max="271" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="268" max="268" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="269" max="269" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="270" max="270" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="271" max="271" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="272" max="272" width="24" bestFit="1" customWidth="1"/>
     <col min="273" max="273" width="11" bestFit="1" customWidth="1"/>
-    <col min="274" max="274" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="275" max="275" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="276" max="276" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="277" max="277" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="274" max="274" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="275" max="275" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="276" max="276" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="277" max="277" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="278" max="279" width="14" bestFit="1" customWidth="1"/>
-    <col min="280" max="280" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="280" max="280" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="281" max="281" width="16" bestFit="1" customWidth="1"/>
-    <col min="282" max="282" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="283" max="283" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="284" max="284" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="285" max="285" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="282" max="282" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="283" max="283" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="284" max="284" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="285" max="285" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="286" max="286" width="16" bestFit="1" customWidth="1"/>
     <col min="287" max="287" width="10" bestFit="1" customWidth="1"/>
-    <col min="288" max="288" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="289" max="289" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="290" max="290" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="291" max="291" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="288" max="288" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="289" max="289" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="290" max="290" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="291" max="291" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="292" max="292" width="12" bestFit="1" customWidth="1"/>
     <col min="293" max="293" width="13" bestFit="1" customWidth="1"/>
     <col min="294" max="294" width="14" bestFit="1" customWidth="1"/>
-    <col min="295" max="295" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="296" max="296" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="297" max="297" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="298" max="298" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="299" max="299" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="300" max="300" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="301" max="301" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="302" max="302" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="303" max="303" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="304" max="304" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="295" max="295" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="296" max="296" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="297" max="297" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="298" max="298" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="299" max="299" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="300" max="300" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="301" max="301" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="302" max="302" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="303" max="303" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="304" max="304" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="305" max="305" width="30" bestFit="1" customWidth="1"/>
-    <col min="306" max="307" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="308" max="308" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="309" max="309" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="310" max="310" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="311" max="311" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="306" max="307" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="308" max="308" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="309" max="309" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="310" max="310" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="311" max="311" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="312" max="312" width="15" bestFit="1" customWidth="1"/>
-    <col min="313" max="313" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="313" max="313" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="314" max="314" width="14" bestFit="1" customWidth="1"/>
-    <col min="315" max="315" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="316" max="316" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="317" max="317" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="315" max="315" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="316" max="316" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="317" max="317" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="318" max="318" width="17" bestFit="1" customWidth="1"/>
-    <col min="319" max="319" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="320" max="321" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="322" max="322" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="323" max="323" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="324" max="324" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="325" max="325" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="319" max="319" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="320" max="321" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="322" max="322" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="323" max="323" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="324" max="324" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="325" max="325" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="326" max="326" width="22" bestFit="1" customWidth="1"/>
-    <col min="327" max="327" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="328" max="328" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="329" max="329" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="330" max="330" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="331" max="331" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="332" max="332" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="333" max="334" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="335" max="335" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="327" max="327" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="328" max="328" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="329" max="329" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="330" max="330" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="331" max="331" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="332" max="332" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="333" max="334" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="335" max="335" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="336" max="336" width="20" bestFit="1" customWidth="1"/>
-    <col min="337" max="337" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="338" max="338" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="339" max="339" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="340" max="340" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="341" max="341" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="342" max="342" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="337" max="337" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="338" max="338" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="339" max="339" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="340" max="340" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="341" max="341" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="342" max="342" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="343" max="343" width="15" bestFit="1" customWidth="1"/>
-    <col min="344" max="344" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="345" max="345" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="346" max="346" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="347" max="347" width="27.83203125" bestFit="1" customWidth="1"/>
-    <col min="348" max="348" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="349" max="349" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="350" max="350" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="351" max="351" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="352" max="352" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="353" max="353" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="354" max="354" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="344" max="344" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="345" max="345" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="346" max="346" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="347" max="347" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="348" max="348" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="349" max="349" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="350" max="350" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="351" max="351" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="352" max="352" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="353" max="353" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="354" max="354" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="355" max="355" width="19" bestFit="1" customWidth="1"/>
-    <col min="356" max="356" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="357" max="357" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="358" max="358" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="356" max="356" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="357" max="357" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="358" max="358" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="359" max="359" width="14" bestFit="1" customWidth="1"/>
-    <col min="360" max="360" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="360" max="360" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="361" max="361" width="12" bestFit="1" customWidth="1"/>
-    <col min="362" max="362" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="363" max="363" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="364" max="364" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="365" max="365" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="366" max="366" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="367" max="367" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="368" max="368" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="369" max="369" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="370" max="370" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="371" max="371" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="372" max="373" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="374" max="374" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="375" max="375" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="377" max="377" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="378" max="378" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="379" max="379" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="380" max="380" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="381" max="381" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="382" max="382" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="383" max="383" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="384" max="384" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="385" max="385" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="386" max="386" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="387" max="387" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="388" max="388" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="389" max="389" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="390" max="391" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="392" max="392" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="393" max="393" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="394" max="394" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="395" max="395" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="396" max="396" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="397" max="397" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="362" max="362" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="363" max="363" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="364" max="364" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="365" max="365" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="366" max="366" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="367" max="367" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="368" max="368" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="369" max="369" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="370" max="370" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="371" max="371" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="372" max="373" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="374" max="374" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="375" max="375" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="377" max="377" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="378" max="378" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="379" max="379" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="380" max="380" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="381" max="381" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="382" max="382" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="383" max="383" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="384" max="384" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="385" max="385" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="386" max="386" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="387" max="387" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="388" max="388" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="389" max="389" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="390" max="391" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="392" max="392" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="393" max="393" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="394" max="394" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="395" max="395" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="396" max="396" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="397" max="397" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="398" max="398" width="16" bestFit="1" customWidth="1"/>
     <col min="399" max="399" width="25" bestFit="1" customWidth="1"/>
-    <col min="400" max="400" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="400" max="400" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="401" max="401" width="17" bestFit="1" customWidth="1"/>
     <col min="402" max="402" width="16" bestFit="1" customWidth="1"/>
-    <col min="403" max="403" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="404" max="404" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="405" max="405" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="406" max="406" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="407" max="407" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="408" max="408" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="409" max="409" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="410" max="410" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="411" max="411" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="412" max="412" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="413" max="413" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="414" max="414" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="415" max="416" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="417" max="417" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="418" max="418" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="403" max="403" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="404" max="404" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="405" max="405" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="406" max="406" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="407" max="407" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="408" max="408" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="409" max="409" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="410" max="410" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="411" max="411" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="412" max="412" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="413" max="413" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="414" max="414" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="415" max="416" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="417" max="417" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="418" max="418" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="419" max="419" width="21" bestFit="1" customWidth="1"/>
-    <col min="420" max="420" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="420" max="420" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="421" max="421" width="17" bestFit="1" customWidth="1"/>
-    <col min="422" max="422" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="423" max="423" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="424" max="424" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="425" max="425" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="426" max="426" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="427" max="427" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="428" max="428" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="429" max="429" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="430" max="430" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="431" max="431" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="432" max="432" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="433" max="433" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="434" max="434" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="435" max="436" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="437" max="437" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="422" max="422" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="423" max="423" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="424" max="424" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="425" max="425" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="426" max="426" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="427" max="427" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="428" max="428" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="429" max="429" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="430" max="430" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="431" max="431" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="432" max="432" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="433" max="433" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="434" max="434" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="435" max="436" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="437" max="437" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="438" max="438" width="18" bestFit="1" customWidth="1"/>
-    <col min="439" max="439" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="440" max="440" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="441" max="441" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="442" max="442" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="443" max="443" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="444" max="444" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="445" max="445" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="446" max="446" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="448" max="448" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="449" max="449" width="40.5" bestFit="1" customWidth="1"/>
-    <col min="450" max="450" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="451" max="451" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="452" max="452" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="439" max="439" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="440" max="440" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="441" max="441" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="442" max="442" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="443" max="443" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="444" max="444" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="445" max="445" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="446" max="446" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="448" max="448" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="449" max="449" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="450" max="450" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="451" max="451" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="452" max="452" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="453" max="453" width="22" bestFit="1" customWidth="1"/>
-    <col min="454" max="454" width="40.1640625" bestFit="1" customWidth="1"/>
-    <col min="455" max="455" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="456" max="456" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="457" max="457" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="458" max="458" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="459" max="459" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="460" max="460" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="461" max="461" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="462" max="462" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="463" max="463" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="464" max="464" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="454" max="454" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="455" max="455" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="456" max="456" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="457" max="457" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="458" max="458" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="459" max="459" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="460" max="460" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="461" max="461" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="462" max="462" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="463" max="463" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="464" max="464" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="465" max="465" width="18" bestFit="1" customWidth="1"/>
-    <col min="466" max="466" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="467" max="467" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="468" max="468" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="469" max="469" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="470" max="470" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="471" max="471" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="472" max="472" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="473" max="473" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="474" max="474" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="475" max="475" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="476" max="476" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="477" max="477" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="466" max="466" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="467" max="467" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="468" max="468" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="469" max="469" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="470" max="470" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="471" max="471" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="472" max="472" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="473" max="473" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="474" max="474" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="475" max="475" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="476" max="476" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="477" max="477" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="478" max="478" width="21" bestFit="1" customWidth="1"/>
     <col min="479" max="479" width="13" bestFit="1" customWidth="1"/>
-    <col min="480" max="480" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="480" max="480" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="481" max="481" width="19" bestFit="1" customWidth="1"/>
-    <col min="482" max="482" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="483" max="483" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="484" max="484" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="482" max="482" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="483" max="483" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="484" max="484" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="485" max="485" width="16" bestFit="1" customWidth="1"/>
     <col min="486" max="486" width="15" bestFit="1" customWidth="1"/>
-    <col min="487" max="487" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="488" max="488" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="489" max="489" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="490" max="490" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="491" max="491" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="492" max="492" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="493" max="493" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="494" max="495" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="487" max="487" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="488" max="488" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="489" max="489" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="490" max="490" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="491" max="491" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="492" max="492" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="493" max="493" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="494" max="495" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="496" max="496" width="11" bestFit="1" customWidth="1"/>
-    <col min="497" max="497" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="498" max="499" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="500" max="500" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="501" max="501" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="502" max="502" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="497" max="497" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="498" max="499" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="500" max="500" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="501" max="501" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="502" max="502" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="503" max="503" width="13" bestFit="1" customWidth="1"/>
-    <col min="504" max="504" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="505" max="506" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="507" max="507" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="508" max="508" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="509" max="510" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="511" max="511" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="512" max="513" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="504" max="504" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="505" max="506" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="507" max="507" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="508" max="508" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="509" max="510" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="511" max="511" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="512" max="513" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="514" max="514" width="17" bestFit="1" customWidth="1"/>
-    <col min="515" max="515" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="516" max="516" width="26.1640625" bestFit="1" customWidth="1"/>
-    <col min="517" max="517" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="518" max="518" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="519" max="519" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="520" max="520" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="521" max="522" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="523" max="523" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="524" max="524" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="525" max="525" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="515" max="515" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="516" max="516" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="517" max="517" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="518" max="518" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="519" max="519" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="520" max="520" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="521" max="522" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="523" max="523" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="524" max="524" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="525" max="525" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="526" max="526" width="17" bestFit="1" customWidth="1"/>
     <col min="527" max="527" width="19" bestFit="1" customWidth="1"/>
-    <col min="528" max="528" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="529" max="529" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="530" max="530" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="528" max="528" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="529" max="529" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="530" max="530" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="531" max="532" width="14" bestFit="1" customWidth="1"/>
-    <col min="533" max="533" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="533" max="533" width="27.28515625" bestFit="1" customWidth="1"/>
     <col min="534" max="534" width="15" bestFit="1" customWidth="1"/>
-    <col min="535" max="535" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="536" max="536" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="537" max="537" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="538" max="538" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="539" max="539" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="540" max="540" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="541" max="541" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="542" max="542" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="543" max="543" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="544" max="544" width="53.6640625" bestFit="1" customWidth="1"/>
-    <col min="545" max="545" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="546" max="546" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="547" max="547" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="535" max="535" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="536" max="536" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="537" max="537" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="538" max="538" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="539" max="539" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="540" max="540" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="541" max="541" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="542" max="542" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="543" max="543" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="544" max="544" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="545" max="545" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="546" max="546" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="547" max="547" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="548" max="548" width="14" bestFit="1" customWidth="1"/>
-    <col min="549" max="549" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="550" max="550" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="551" max="551" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="549" max="549" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="550" max="550" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="551" max="551" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="552" max="552" width="15" bestFit="1" customWidth="1"/>
-    <col min="553" max="553" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="554" max="555" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="556" max="556" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="557" max="557" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="558" max="558" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="559" max="559" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="560" max="560" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="561" max="561" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="553" max="553" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="554" max="555" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="556" max="556" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="557" max="557" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="558" max="558" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="559" max="559" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="560" max="560" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="561" max="561" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="562" max="562" width="18" bestFit="1" customWidth="1"/>
-    <col min="563" max="563" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="563" max="563" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="564" max="564" width="13" bestFit="1" customWidth="1"/>
-    <col min="565" max="565" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="566" max="566" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="567" max="567" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="568" max="568" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="569" max="569" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="565" max="565" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="566" max="566" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="567" max="567" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="568" max="568" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="569" max="569" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="570" max="570" width="23" bestFit="1" customWidth="1"/>
-    <col min="571" max="571" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="572" max="572" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="573" max="575" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="571" max="571" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="572" max="572" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="573" max="575" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="576" max="576" width="16" bestFit="1" customWidth="1"/>
-    <col min="577" max="577" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="578" max="578" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="577" max="577" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="578" max="578" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="579" max="579" width="16" bestFit="1" customWidth="1"/>
-    <col min="580" max="580" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="581" max="581" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="582" max="582" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="583" max="583" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="584" max="584" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="585" max="585" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="580" max="580" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="581" max="581" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="582" max="582" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="583" max="583" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="584" max="584" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="585" max="585" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="586" max="586" width="14" bestFit="1" customWidth="1"/>
-    <col min="587" max="587" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="588" max="588" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="587" max="587" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="588" max="588" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="589" max="589" width="24" bestFit="1" customWidth="1"/>
-    <col min="590" max="590" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="591" max="591" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="590" max="590" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="591" max="591" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="592" max="592" width="17" bestFit="1" customWidth="1"/>
     <col min="593" max="593" width="14" bestFit="1" customWidth="1"/>
-    <col min="594" max="594" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="595" max="595" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="596" max="596" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="597" max="597" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="598" max="598" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="599" max="599" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="600" max="600" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="601" max="601" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="594" max="594" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="595" max="595" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="596" max="596" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="597" max="597" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="598" max="598" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="599" max="599" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="600" max="600" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="601" max="601" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="602" max="602" width="17" bestFit="1" customWidth="1"/>
-    <col min="603" max="603" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="604" max="604" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="605" max="605" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="606" max="606" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="603" max="603" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="604" max="604" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="605" max="605" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="606" max="606" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="607" max="607" width="21" bestFit="1" customWidth="1"/>
-    <col min="608" max="608" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="609" max="609" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="610" max="610" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="611" max="611" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="612" max="612" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="613" max="613" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="614" max="614" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="608" max="608" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="609" max="609" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="610" max="610" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="611" max="611" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="612" max="612" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="613" max="613" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="614" max="614" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="615" max="615" width="15" bestFit="1" customWidth="1"/>
-    <col min="616" max="616" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="617" max="617" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="618" max="618" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="616" max="616" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="617" max="617" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="618" max="618" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="619" max="619" width="20" bestFit="1" customWidth="1"/>
     <col min="620" max="620" width="18" bestFit="1" customWidth="1"/>
-    <col min="621" max="621" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="622" max="622" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="623" max="623" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="624" max="624" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="625" max="625" width="27.1640625" bestFit="1" customWidth="1"/>
-    <col min="626" max="627" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="628" max="628" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="629" max="629" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="630" max="630" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="631" max="631" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="632" max="632" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="633" max="633" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="634" max="635" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="621" max="621" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="622" max="622" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="623" max="623" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="624" max="624" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="625" max="625" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="626" max="627" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="628" max="628" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="629" max="629" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="630" max="630" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="631" max="631" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="632" max="632" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="633" max="633" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="634" max="635" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>487</v>
       </c>
@@ -33292,155 +33395,155 @@
         <v>488</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>1223</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>1224</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>1218</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>1222</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13">
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>1226</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14">
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>1219</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>1225</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>1221</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>978</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19">
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>1220</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20">
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22">
         <v>636</v>
       </c>
     </row>

--- a/Elenco_Concorso_TOTALE_marzo 2026.xlsx
+++ b/Elenco_Concorso_TOTALE_marzo 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g.moroni\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\guido\projects\mokador-concorso2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC92BD3-52E9-409D-BBC4-F9B0EEEE2DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1627B96D-6301-493B-89C2-6BA312CA1580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{823CA8BD-5CB5-43A5-84D0-940CC410799D}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4495" uniqueCount="2595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4529" uniqueCount="2604">
   <si>
     <t>B &amp; B di BRANDOLINI ENRICO E C. SAS</t>
   </si>
@@ -7818,6 +7818,33 @@
   </si>
   <si>
     <t>SAN LAZZARO DI SAVENA</t>
+  </si>
+  <si>
+    <t>BAR CASA DI CURA DOMUS SALUTIS</t>
+  </si>
+  <si>
+    <t>VIA LAZZARETTO, 3</t>
+  </si>
+  <si>
+    <t>BAR CANOSSA CAMPUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VIA ALEARDO ALEARDI, 14</t>
+  </si>
+  <si>
+    <t>VIA GUIDO GHEDINI</t>
+  </si>
+  <si>
+    <t>NEGRAR DI VALPOLICELLA</t>
+  </si>
+  <si>
+    <t>BAR CAMPUS CATTOLICA GARZETTA</t>
+  </si>
+  <si>
+    <t>VIA GARZETTA, 38</t>
+  </si>
+  <si>
+    <t>BAR OSPEDALE NEGRAR</t>
   </si>
 </sst>
 </file>
@@ -7920,7 +7947,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7977,9 +8004,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -16116,14 +16140,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147308C3-0088-488A-BBC3-4C05F360FB79}">
-  <dimension ref="A1:H643"/>
+  <dimension ref="A1:H646"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="123.42578125" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
     <col min="6" max="6" width="51.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -32695,25 +32719,25 @@
       <c r="A638" s="6" t="s">
         <v>1224</v>
       </c>
-      <c r="B638" s="22">
+      <c r="B638" s="21">
         <v>12274</v>
       </c>
-      <c r="C638" s="23" t="s">
+      <c r="C638" s="22" t="s">
         <v>2589</v>
       </c>
-      <c r="D638" s="23" t="s">
+      <c r="D638" s="22" t="s">
         <v>2590</v>
       </c>
-      <c r="E638" s="23" t="s">
+      <c r="E638" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="F638" s="23" t="s">
+      <c r="F638" s="22" t="s">
         <v>2591</v>
       </c>
-      <c r="G638" s="23" t="s">
+      <c r="G638" s="22" t="s">
         <v>1058</v>
       </c>
-      <c r="H638" s="23" t="s">
+      <c r="H638" s="22" t="s">
         <v>554</v>
       </c>
     </row>
@@ -32721,25 +32745,25 @@
       <c r="A639" s="6" t="s">
         <v>1224</v>
       </c>
-      <c r="B639" s="22">
+      <c r="B639" s="21">
         <v>12274</v>
       </c>
-      <c r="C639" s="23" t="s">
+      <c r="C639" s="22" t="s">
         <v>2589</v>
       </c>
-      <c r="D639" s="23" t="s">
+      <c r="D639" s="22" t="s">
         <v>2592</v>
       </c>
-      <c r="E639" s="23" t="s">
+      <c r="E639" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="F639" s="23" t="s">
+      <c r="F639" s="22" t="s">
         <v>2593</v>
       </c>
       <c r="G639" t="s">
         <v>2594</v>
       </c>
-      <c r="H639" s="23" t="s">
+      <c r="H639" s="22" t="s">
         <v>554</v>
       </c>
     </row>
@@ -32747,25 +32771,144 @@
       <c r="A640" s="6" t="s">
         <v>1224</v>
       </c>
-    </row>
-    <row r="641" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C640" s="22" t="s">
+        <v>2589</v>
+      </c>
+      <c r="E640" s="22" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="6" t="s">
         <v>1224</v>
       </c>
-    </row>
-    <row r="642" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C641" s="22" t="s">
+        <v>2589</v>
+      </c>
+      <c r="E641" s="22" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="6" t="s">
         <v>1224</v>
       </c>
-    </row>
-    <row r="643" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A643" s="21"/>
+      <c r="C642" s="22" t="s">
+        <v>2589</v>
+      </c>
+      <c r="E642" s="22" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="643" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A643" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B643">
+        <v>12274</v>
+      </c>
+      <c r="C643" s="22" t="s">
+        <v>2589</v>
+      </c>
+      <c r="D643" t="s">
+        <v>2595</v>
+      </c>
+      <c r="E643" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="F643" t="s">
+        <v>2596</v>
+      </c>
+      <c r="G643" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H643" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="644" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A644" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B644" s="21">
+        <v>12274</v>
+      </c>
+      <c r="C644" s="22" t="s">
+        <v>2589</v>
+      </c>
+      <c r="D644" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E644" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="F644" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G644" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H644" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="645" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A645" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B645" s="21">
+        <v>12274</v>
+      </c>
+      <c r="C645" s="22" t="s">
+        <v>2589</v>
+      </c>
+      <c r="D645" t="s">
+        <v>2603</v>
+      </c>
+      <c r="E645" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="F645" t="s">
+        <v>2599</v>
+      </c>
+      <c r="G645" t="s">
+        <v>2600</v>
+      </c>
+      <c r="H645" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="646" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A646" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B646" s="21">
+        <v>12274</v>
+      </c>
+      <c r="C646" s="22" t="s">
+        <v>2589</v>
+      </c>
+      <c r="D646" t="s">
+        <v>2601</v>
+      </c>
+      <c r="E646" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="F646" t="s">
+        <v>2602</v>
+      </c>
+      <c r="G646" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H646" t="s">
+        <v>1964</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H280" xr:uid="{147308C3-0088-488A-BBC3-4C05F360FB79}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H6410">
-    <sortCondition ref="A2:A6410"/>
-    <sortCondition ref="C2:C6410"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H6406">
+    <sortCondition ref="A2:A6406"/>
+    <sortCondition ref="C2:C6406"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>

--- a/Elenco_Concorso_TOTALE_marzo 2026.xlsx
+++ b/Elenco_Concorso_TOTALE_marzo 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\guido\projects\mokador-concorso2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1627B96D-6301-493B-89C2-6BA312CA1580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0007F8-931A-4AC2-8425-6AA5F40F7DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{823CA8BD-5CB5-43A5-84D0-940CC410799D}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4529" uniqueCount="2604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4520" uniqueCount="2604">
   <si>
     <t>B &amp; B di BRANDOLINI ENRICO E C. SAS</t>
   </si>
@@ -16140,7 +16140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147308C3-0088-488A-BBC3-4C05F360FB79}">
-  <dimension ref="A1:H646"/>
+  <dimension ref="A1:H643"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="123.42578125" customWidth="1"/>
@@ -32741,7 +32741,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="639" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" s="6" t="s">
         <v>1224</v>
       </c>
@@ -32767,140 +32767,107 @@
         <v>554</v>
       </c>
     </row>
-    <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" s="6" t="s">
         <v>1224</v>
       </c>
+      <c r="B640">
+        <v>12274</v>
+      </c>
       <c r="C640" s="22" t="s">
         <v>2589</v>
       </c>
+      <c r="D640" t="s">
+        <v>2595</v>
+      </c>
       <c r="E640" s="22" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F640" t="s">
+        <v>2596</v>
+      </c>
+      <c r="G640" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H640" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" s="6" t="s">
         <v>1224</v>
       </c>
+      <c r="B641" s="21">
+        <v>12274</v>
+      </c>
       <c r="C641" s="22" t="s">
         <v>2589</v>
       </c>
+      <c r="D641" t="s">
+        <v>2597</v>
+      </c>
       <c r="E641" s="22" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F641" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G641" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H641" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" s="6" t="s">
         <v>1224</v>
       </c>
+      <c r="B642" s="21">
+        <v>12274</v>
+      </c>
       <c r="C642" s="22" t="s">
         <v>2589</v>
       </c>
+      <c r="D642" t="s">
+        <v>2603</v>
+      </c>
       <c r="E642" s="22" t="s">
         <v>285</v>
+      </c>
+      <c r="F642" t="s">
+        <v>2599</v>
+      </c>
+      <c r="G642" t="s">
+        <v>2600</v>
+      </c>
+      <c r="H642" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" s="6" t="s">
         <v>1224</v>
       </c>
-      <c r="B643">
+      <c r="B643" s="21">
         <v>12274</v>
       </c>
       <c r="C643" s="22" t="s">
         <v>2589</v>
       </c>
       <c r="D643" t="s">
-        <v>2595</v>
+        <v>2601</v>
       </c>
       <c r="E643" s="22" t="s">
         <v>285</v>
       </c>
       <c r="F643" t="s">
-        <v>2596</v>
+        <v>2602</v>
       </c>
       <c r="G643" t="s">
         <v>1982</v>
       </c>
       <c r="H643" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="644" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A644" s="6" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B644" s="21">
-        <v>12274</v>
-      </c>
-      <c r="C644" s="22" t="s">
-        <v>2589</v>
-      </c>
-      <c r="D644" t="s">
-        <v>2597</v>
-      </c>
-      <c r="E644" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="F644" t="s">
-        <v>2598</v>
-      </c>
-      <c r="G644" t="s">
-        <v>1982</v>
-      </c>
-      <c r="H644" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A645" s="6" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B645" s="21">
-        <v>12274</v>
-      </c>
-      <c r="C645" s="22" t="s">
-        <v>2589</v>
-      </c>
-      <c r="D645" t="s">
-        <v>2603</v>
-      </c>
-      <c r="E645" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="F645" t="s">
-        <v>2599</v>
-      </c>
-      <c r="G645" t="s">
-        <v>2600</v>
-      </c>
-      <c r="H645" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="646" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A646" s="6" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B646" s="21">
-        <v>12274</v>
-      </c>
-      <c r="C646" s="22" t="s">
-        <v>2589</v>
-      </c>
-      <c r="D646" t="s">
-        <v>2601</v>
-      </c>
-      <c r="E646" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="F646" t="s">
-        <v>2602</v>
-      </c>
-      <c r="G646" t="s">
-        <v>1982</v>
-      </c>
-      <c r="H646" t="s">
         <v>1964</v>
       </c>
     </row>
